--- a/data/accounts.xlsx
+++ b/data/accounts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dannelson/Desktop/we-serve/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A3E81F-3A05-0841-B9D2-08A7F3C1EDD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3501C66-3E16-8D49-8F85-6D7A022D17B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{2060A397-D908-2B4C-B73B-57C2CD1CEBA5}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13500" windowHeight="21600" xr2:uid="{2060A397-D908-2B4C-B73B-57C2CD1CEBA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Resources" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="AccountsChart">Resources!$A$1:$B$71</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,6 +30,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
